--- a/data kemiringan robot pitch double support (invers).xlsx
+++ b/data kemiringan robot pitch double support (invers).xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,19 +465,19 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>-6.111</v>
+        <v>-8.951000000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>-38.642</v>
+        <v>-38.633</v>
       </c>
       <c r="D2" t="n">
-        <v>195.192</v>
+        <v>195.082</v>
       </c>
       <c r="E2" t="n">
-        <v>-111.809</v>
+        <v>-1.395</v>
       </c>
       <c r="F2" t="n">
-        <v>2.023</v>
+        <v>4.668</v>
       </c>
     </row>
     <row r="3">
@@ -485,19 +485,479 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>-11.814</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>-38.641</v>
+        <v>-38.819</v>
       </c>
       <c r="D3" t="n">
-        <v>194.975</v>
+        <v>195.146</v>
       </c>
       <c r="E3" t="n">
-        <v>3.718</v>
+        <v>1.815</v>
       </c>
       <c r="F3" t="n">
-        <v>1.692</v>
+        <v>3.849</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-14.024</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-38.818</v>
+      </c>
+      <c r="D4" t="n">
+        <v>194.906</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2.879</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-16.858</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-38.818</v>
+      </c>
+      <c r="D5" t="n">
+        <v>194.658</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10.561</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.995</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-19.712</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-38.818</v>
+      </c>
+      <c r="D6" t="n">
+        <v>194.413</v>
+      </c>
+      <c r="E6" t="n">
+        <v>7.612</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4.075</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-25.38</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-38.817</v>
+      </c>
+      <c r="D7" t="n">
+        <v>193.723</v>
+      </c>
+      <c r="E7" t="n">
+        <v>7.494</v>
+      </c>
+      <c r="F7" t="n">
+        <v>4.066</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-25.43</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-38.816</v>
+      </c>
+      <c r="D8" t="n">
+        <v>193.826</v>
+      </c>
+      <c r="E8" t="n">
+        <v>8.955</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3.748</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-31.073</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-38.815</v>
+      </c>
+      <c r="D9" t="n">
+        <v>192.936</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12.812</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3.658</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-31.098</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-38.815</v>
+      </c>
+      <c r="D10" t="n">
+        <v>192.988</v>
+      </c>
+      <c r="E10" t="n">
+        <v>13.053</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3.875</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-36.708</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-38.814</v>
+      </c>
+      <c r="D11" t="n">
+        <v>191.902</v>
+      </c>
+      <c r="E11" t="n">
+        <v>12.91</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4.546</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-39.511</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-38.822</v>
+      </c>
+      <c r="D12" t="n">
+        <v>191.311</v>
+      </c>
+      <c r="E12" t="n">
+        <v>15.912</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.954</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-43.892</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-38.821</v>
+      </c>
+      <c r="D13" t="n">
+        <v>189.904</v>
+      </c>
+      <c r="E13" t="n">
+        <v>15.639</v>
+      </c>
+      <c r="F13" t="n">
+        <v>5.828</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>0</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-11.138</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-38.828</v>
+      </c>
+      <c r="D14" t="n">
+        <v>194.999</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2.563</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3.089</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-8.300000000000001</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-38.828</v>
+      </c>
+      <c r="D15" t="n">
+        <v>195.146</v>
+      </c>
+      <c r="E15" t="n">
+        <v>4.122</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3.804</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>-2</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-2.41</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-38.828</v>
+      </c>
+      <c r="D16" t="n">
+        <v>195.102</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-116.79</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.739</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>-3</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-2.385</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-38.828</v>
+      </c>
+      <c r="D17" t="n">
+        <v>195.051</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-135.215</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3.515</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>-4</v>
+      </c>
+      <c r="B18" t="n">
+        <v>3.316</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-38.829</v>
+      </c>
+      <c r="D18" t="n">
+        <v>194.938</v>
+      </c>
+      <c r="E18" t="n">
+        <v>147.224</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3.206</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>-5</v>
+      </c>
+      <c r="B19" t="n">
+        <v>6.176</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-38.829</v>
+      </c>
+      <c r="D19" t="n">
+        <v>194.781</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-3.908</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3.522</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>-6</v>
+      </c>
+      <c r="B20" t="n">
+        <v>10.11</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-38.649</v>
+      </c>
+      <c r="D20" t="n">
+        <v>194.85</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-2.326</v>
+      </c>
+      <c r="F20" t="n">
+        <v>3.71</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>-7</v>
+      </c>
+      <c r="B21" t="n">
+        <v>12.968</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-38.65</v>
+      </c>
+      <c r="D21" t="n">
+        <v>194.575</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-7.542</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-116.289</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>-8</v>
+      </c>
+      <c r="B22" t="n">
+        <v>18.983</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-38.829</v>
+      </c>
+      <c r="D22" t="n">
+        <v>194.349</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-4.143</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-12.162</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>-9</v>
+      </c>
+      <c r="B23" t="n">
+        <v>21.805</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-38.829</v>
+      </c>
+      <c r="D23" t="n">
+        <v>193.97</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-10.243</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.941</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>-10</v>
+      </c>
+      <c r="B24" t="n">
+        <v>26.792</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-38.653</v>
+      </c>
+      <c r="D24" t="n">
+        <v>193.165</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-9.199999999999999</v>
+      </c>
+      <c r="F24" t="n">
+        <v>3.102</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>-11</v>
+      </c>
+      <c r="B25" t="n">
+        <v>30.25</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-38.654</v>
+      </c>
+      <c r="D25" t="n">
+        <v>192.631</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-12.496</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.906</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>-12</v>
+      </c>
+      <c r="B26" t="n">
+        <v>32.449</v>
+      </c>
+      <c r="C26" t="n">
+        <v>-38.655</v>
+      </c>
+      <c r="D26" t="n">
+        <v>191.928</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-13.729</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-8.192</v>
       </c>
     </row>
   </sheetData>
